--- a/data/ECB/Annotated/ecb_Press Conference Statements + Q&A_to_annotate.xlsx
+++ b/data/ECB/Annotated/ecb_Press Conference Statements + Q&A_to_annotate.xlsx
@@ -1,25 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzouberti/Desktop/BANQUE DE FRANCE /Data Folders/ECB BRANCH/Press Conference Statements + Q&amp;A/press-conference-statements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzouberti/Desktop/BANQUE DE FRANCE /Github Repos/Project/BdF-Project/data/ECB/Annotated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376E65D7-4044-D14C-B78F-310AEF1DE6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32869F04-4B9E-9B47-9B46-5E3B87C11A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2720" yWindow="-21000" windowWidth="33600" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2720" yWindow="-20500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4946" uniqueCount="1674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4935" uniqueCount="1669">
   <si>
     <t>date</t>
   </si>
@@ -5044,21 +5040,6 @@
   </si>
   <si>
     <t xml:space="preserve">N </t>
-  </si>
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Sum of Column2</t>
   </si>
 </sst>
 </file>
@@ -5117,16 +5098,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5142,1100 +5118,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[ecb_to_annotate.xlsx]Sheet2!PivotTable1</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet2!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet2!$A$2:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>D</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>H</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>N </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet2!$B$2:$B$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>280</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>199</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>506</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F597-B44D-B3A8-33318CABE681}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="834635280"/>
-        <c:axId val="834637264"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="834635280"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="834637264"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="834637264"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="834635280"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5FC0008-C044-1614-8114-F2EE98B32CEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lorenzo Uberti" refreshedDate="46230.628518518519" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{2A86F84A-161F-7C4D-9E03-F770A014B0E8}">
-  <cacheSource type="worksheet">
-    <worksheetSource name="Table1"/>
-  </cacheSource>
-  <cacheFields count="2">
-    <cacheField name="Column1" numFmtId="0">
-      <sharedItems count="3">
-        <s v="N "/>
-        <s v="H"/>
-        <s v="D"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Column2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="199" maxValue="506"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="3">
-  <r>
-    <x v="0"/>
-    <n v="506"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <n v="199"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <n v="280"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7231161D-16D6-1A4B-9315-B7DA8B3AF72F}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A1:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Column2" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB4C941C-87CE-6B41-B6F8-6A5EEF200D68}" name="Table1" displayName="Table1" ref="G2:H5" totalsRowShown="0">
-  <autoFilter ref="G2:H5" xr:uid="{CB4C941C-87CE-6B41-B6F8-6A5EEF200D68}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AA6A2B72-57BF-9941-9C58-CB27020AEAD6}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{A94CF65E-0BE6-934D-BB34-CBA75276AB2C}" name="Column2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6524,63 +5406,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DDF15E-0F8A-A646-9CD6-03BFB05C5461}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>1671</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>1666</v>
-      </c>
-      <c r="B2" s="4">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>1667</v>
-      </c>
-      <c r="B3" s="4">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>1668</v>
-      </c>
-      <c r="B4" s="4">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>1672</v>
-      </c>
-      <c r="B5" s="4">
-        <v>985</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H987"/>
+  <dimension ref="A1:E987"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.1640625" customWidth="1"/>
@@ -6590,7 +5417,7 @@
     <col min="7" max="8" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6607,7 +5434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6623,14 +5450,8 @@
       <c r="E2" t="s">
         <v>1665</v>
       </c>
-      <c r="G2" t="s">
-        <v>1669</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1670</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -6646,15 +5467,8 @@
       <c r="E3" t="s">
         <v>1665</v>
       </c>
-      <c r="G3" t="s">
-        <v>1668</v>
-      </c>
-      <c r="H3">
-        <f>COUNTIF(E2:E987, "N")</f>
-        <v>506</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -6670,15 +5484,8 @@
       <c r="E4" t="s">
         <v>1665</v>
       </c>
-      <c r="G4" t="s">
-        <v>1667</v>
-      </c>
-      <c r="H4">
-        <f>COUNTIF(E2:E987, "H")</f>
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -6694,15 +5501,8 @@
       <c r="E5" t="s">
         <v>1665</v>
       </c>
-      <c r="G5" t="s">
-        <v>1666</v>
-      </c>
-      <c r="H5">
-        <f>COUNTIF(E2:E987, "D")</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6719,7 +5519,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6736,7 +5536,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6753,7 +5553,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -6770,7 +5570,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -6787,7 +5587,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -6804,7 +5604,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -6821,7 +5621,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -6838,7 +5638,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -6855,7 +5655,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -6872,7 +5672,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -23398,8 +22198,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>